--- a/artfynd/A 56592-2023 artfynd.xlsx
+++ b/artfynd/A 56592-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56592-2023 artfynd.xlsx
+++ b/artfynd/A 56592-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109173167</v>
+        <v>120989022</v>
       </c>
       <c r="B2" t="n">
-        <v>97924</v>
+        <v>106199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224365</v>
+        <v>221154</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Byskedammet cirka 500 m S-SSV, Nb</t>
+          <t>Cirka 500 m S-SSV om Byskedammet, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -779,6 +779,228 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114144429</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99872</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222316</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Klotstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex globularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Byskedammet ca 500 m S-SSV, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>767201</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7252860</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1992-07-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1992-07-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>stig över skogsmyr</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lennart Stenberg, Nenita Thörn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109173167</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98065</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224365</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Riplummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Grev. &amp; Hook.) Selander</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Byskedammet cirka 500 m S-SSV, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>767201</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7252860</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1992-07-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1992-07-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>stig över skogsmyr</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Stenberg, Nenita Thörn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
         </is>

--- a/artfynd/A 56592-2023 artfynd.xlsx
+++ b/artfynd/A 56592-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120989022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114144429</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109173167</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>